--- a/outputs/resultats/bnc/2026_t2_vs_2026_t1/text_comparison.xlsx
+++ b/outputs/resultats/bnc/2026_t2_vs_2026_t1/text_comparison.xlsx
@@ -1300,7 +1300,11 @@
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>jhjkh</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">

--- a/outputs/resultats/bnc/2026_t2_vs_2026_t1/text_comparison.xlsx
+++ b/outputs/resultats/bnc/2026_t2_vs_2026_t1/text_comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analyse complète" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analyse complète'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analyse complète'!$A$1:$J$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Nouvelle mention réglementaire, risque climatique / ESG, information ajoutée.
-Ce qui change : Le T2 ajoute une nouvelle information sur la législation 'Omnibus' de la Commission européenne et son impact potentiel sur la divulgation en matière de durabilité.
+Ce qui change : Le T2 ajoute une divulgation sur la législation « Omnibus » de la Commission européenne et son impact sur la directive CSRD, absente au T1.
 Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
@@ -596,7 +596,7 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Nouvelle mention réglementaire, risque climatique / ESG, information ajoutée.
-Ce qui change : Le T2 ajoute une nouvelle information sur l'exposé sondage du CCNID concernant les modifications de la NCID.
+Ce qui change : Le T2 ajoute une divulgation sur les modifications proposées par le CCNID concernant les informations à fournir en lien avec les émissions de gaz à effet de serre, absente au T1.
 Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
@@ -641,9 +641,9 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Information retirée, exigences réglementaires.
-Ce qui change : La sous-section sur les exigences de communication publique pour les banques d'importance systémique mondiale a été supprimée.
-Pertinence métier : Ce changement met l'accent sur la réduction de la transparence des informations fournies sur les exigences de communication publique. Le retrait de cette sous-section peut affecter la compréhension des attentes réglementaires et la comparabilité des pratiques de divulgation entre institutions financières.
-Point de surveillance : Exigences réglementaires — Le changement indique une réduction de la transparence des informations sur les exigences de communication publique. Ce point permet de suivre l'évolution des pratiques de divulgation et la conformité aux attentes réglementaires.</t>
+Ce qui change : Le T2 retire la sous-section sur les exigences de communication publique pour les banques d'importance systémique mondiale, présente au T1.
+Pertinence métier : Ce changement met l'accent sur la réduction de la divulgation relative aux exigences de communication publique pour les banques d'importance systémique mondiale. Le retrait de cette information modifie la lecture de la transparence de la banque sur ses obligations réglementaires, ce qui est crucial pour la comparabilité entre pairs.
+Point de surveillance : Exigences réglementaires — Le changement indique un retrait de la divulgation sur les exigences de communication publique pour les banques d'importance systémique mondiale. Ce point permet de suivre l'évolution de la transparence de la banque sur ses obligations réglementaires et la comparabilité de sa divulgation avec les autres institutions.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Revenus de négociation et de souscription quotidiens</t>
+          <t>VaR des portefeuilles de négociation (1) (2)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -664,18 +664,26 @@
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Le graphique suivant illustre les revenus de négociation et de souscription ainsi que la VaR sur une base quotidienne. Les revenus de négociation et de souscription quotidiens ont été positifs pendant 93 % des jours du trimestre terminé le 31 janvier 2026. De plus, quatre jours ont été marqués par des pertes nettes de négociation et de souscription quotidiennes supérieures à 1 M$. Aucune de ces pertes n'excédait la VaR.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>La moyenne de la VaR totale des portefeuilles de négociation est demeurée relativement stable entre le quatrième trimestre de 2025 et le premier trimestre de 2026.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>La moyenne de la VaR totale des portefeuilles de négociation a diminué entre le premier et le deuxième trimestre de 2026, principalement en raison d'une baisse du risque de taux d'intérêt.</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Oui</t>
@@ -684,10 +692,10 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Information retirée, structure du rapport.
-Ce qui change : La sous-section sur les revenus de négociation et de souscription quotidiens a été supprimée.
-Pertinence métier : Ce changement met en évidence une réduction de la transparence concernant les performances de négociation, ce qui peut affecter la compréhension des risques associés aux activités de négociation. La suppression de cette information modifie la structure du rapport et peut influencer la perception des performances financières.
-Point de surveillance : Structure du rapport — Le retrait de cette section nécessite une attention particulière pour évaluer l'impact sur la transparence et la comparabilité des performances de négociation.</t>
+Sujet détecté : Texte de risque modifié, hypothèses ou explications de risque.
+Ce qui change : Le T2 précise que la diminution de la mesure de risque de marché est principalement due à une baisse du risque de taux d'intérêt, ce qui n'était pas mentionné au T1.
+Pertinence métier : Ce changement met en évidence une révision des explications fournies par la banque concernant la gestion de son risque de marché. La mention explicite de la baisse du risque de taux d'intérêt modifie la lecture de l'exposition au risque et la transparence de la banque sur ses facteurs de risque.
+Point de surveillance : Risque de marché — Le changement indique que la banque ajuste ses explications sur la variation de la mesure de risque de marché. Ce point permet de suivre l'évolution de la transparence de la banque sur ses risques de marché et la comparabilité de sa divulgation avec les autres institutions.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -695,195 +703,195 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>intro</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>La politique de gestion du capital de la Banque définit les principes directeurs ainsi que les rôles et responsabilités à l'égard de son processus interne d'évaluation de l'adéquation des fonds propres. Ce processus vise à déterminer le niveau des fonds propres dont la Banque doit disposer afin de poursuivre ses activités d'affaires et de faire face aux pertes non prévues découlant de conditions économiques et opérationnelles extrêmement difficiles. Plus de détails sur le cadre de gestion du capital sont présentés dans la section « Gestion du capital » du Rapport annuel 2025 aux pages 62 à 71.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>La Banque gère son capital conformément au cadre de gestion du capital qui est décrit dans la section « Gestion du capital » du Rapport annuel 2025 aux pages 62 à 71.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, fonds propres réglementaires.
+Ce qui change : Le T2 simplifie la description du cadre de gestion du capital, supprimant des détails sur le processus interne d'évaluation des fonds propres et les pertes non prévues.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>L'actif pondéré en fonction des risques a augmenté de 0,6 G$ pour s'établir à 189,4 G$ au 31 janvier 2026, comparativement à 188,8 G$ au 31 octobre 2025, une augmentation de 0,6 G$ qui s'explique principalement par la croissance organique de l'actif pondéré en fonction des risques atténuée par la variation du taux de change.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>L'actif pondéré en fonction des risques a augmenté de 5,7 G$ pour s'établir à 194,5 G$ au 30 avril 2026, comparativement à 188,8 G$ au 31 octobre 2025. Cette augmentation découle de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts atténuées par la variation du taux de change.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié, fonds propres réglementaires.
+Ce qui change : Le T2 ajoute la détérioration de la qualité de crédit comme facteur d'augmentation de l'actif pondéré en fonction des risques, absente au T1.
+Pertinence métier : Ce changement met en évidence un nouveau facteur de risque influençant l'actif pondéré en fonction des risques, ce qui peut affecter la compréhension des risques liés aux fonds propres réglementaires. L'ajout de la détérioration de la qualité de crédit modifie la lecture des facteurs influençant l'actif pondéré en fonction des risques.
+Point de surveillance : Fonds propres réglementaires — Le changement indique l'ajout d'un nouveau facteur de risque influençant l'actif pondéré en fonction des risques. Ce point permet de suivre l'évolution de la compréhension des risques liés aux fonds propres réglementaires.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Gestion des risques</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Revenus de négociation et de souscription quotidiens</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Le graphique suivant illustre les revenus de négociation et de souscription ainsi que la VaR sur une base quotidienne. Les revenus de négociation et de souscription quotidiens ont été positifs pendant 93 % des jours du trimestre terminé le 31 janvier 2026. De plus, quatre jours ont été marqués par des pertes nettes de négociation et de souscription quotidiennes supérieures à 1 M$. Aucune de ces pertes n'excédait la VaR.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Structure du rapport, information retirée.
+Ce qui change : Le T2 retire une sous-section sur les revenus de négociation et de souscription quotidiens, présente au T1.
+Pertinence métier : Ce changement met l'accent sur la modification de la structure du rapport et la réduction de la transparence sur les performances de négociation de la banque. Le retrait d'une section entière peut affecter la compréhension des activités de négociation et la comparabilité avec les pairs.
+Point de surveillance : Structure du rapport — Le changement indique que la banque réduit la divulgation de ses performances de négociation. Ce point permet de suivre l'évolution de la transparence de la banque sur ses activités de négociation et la comparabilité de sa divulgation avec les autres institutions.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 31 janvier 2026, ainsi que les données comparatives au 31 octobre 2025. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.
 Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de sa clientèle représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.
 La Banque a également des engagements minimaux futurs, en vertu de contrats de location, et d'autres contrats, principalement liés à des engagements d'achat de prêts et à des services informatiques impartis.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Information retirée, structure du rapport.
-Ce qui change : La sous-section sur les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan a été supprimée.
+Sujet détecté : Structure du rapport, information retirée.
+Ce qui change : Le T2 retire une sous-section sur les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan, présente au T1.
 Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Risque environnemental et social</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>La Banque surveille de près l'évolution de la réglementation et participe activement aux divers processus de consultation. En outre, depuis le 1 er novembre 2025, le fait nouveau en matière de réglementation suivant est à considérer.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>La Banque surveille de près l'évolution de la réglementation et participe aux divers processus de consultation. En outre, depuis le 1 er novembre 2025, les faits nouveaux en matière de réglementation suivants sont à considérer.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Nouvelle mention réglementaire, exigences réglementaires.
-Ce qui change : Le T2 indique plusieurs faits nouveaux en matière de réglementation, alors qu'un seul était mentionné au T1.
-Pertinence métier : Ce changement met en évidence une évolution des exigences réglementaires qui peuvent influencer la conformité et la gestion des risques de la banque. La mention de plusieurs faits nouveaux souligne l'importance de suivre l'évolution réglementaire pour s'assurer que la banque reste alignée avec les attentes prudentielles.
-Point de surveillance : Exigences réglementaires — Le changement indique que la banque doit surveiller plusieurs évolutions réglementaires, ce qui nécessite une attention particulière pour évaluer l'impact sur la conformité et la gestion des risques.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>VaR des portefeuilles de négociation (1) (2)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>La moyenne de la VaR totale des portefeuilles de négociation est demeurée relativement stable entre le quatrième trimestre de 2025 et le premier trimestre de 2026.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>La moyenne de la VaR totale des portefeuilles de négociation a diminué entre le premier et le deuxième trimestre de 2026, principalement en raison d'une baisse du risque de taux d'intérêt.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Texte de risque modifié, hypothèses de risque.
-Ce qui change : La stabilité de la mesure de risque de marché est remplacée par une diminution, avec une explication liée au risque de taux d'intérêt.
-Pertinence métier : Ce changement met l'accent sur l'évolution des risques de marché, en particulier le risque de taux d'intérêt, qui est crucial pour la gestion des portefeuilles de négociation. La modification de la mesure de risque et l'ajout d'une explication sur le risque de taux d'intérêt influencent la perception du risque et la stratégie de gestion.
-Point de surveillance : Risque de marché — Le changement indique une variation dans la perception du risque de marché, nécessitant une attention particulière sur les facteurs influençant cette mesure, notamment le risque de taux d'intérêt.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Exigences - Ratios des fonds propres (1) , de levier (1) et TLAC (2) réglementaires</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Le tableau suivant présente les exigences minimales de fonds propres établies par le BSIF.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Information ajoutée, fonds propres réglementaires.
-Ce qui change : Le T2 ajoute un tableau présentant les exigences minimales de fonds propres établies par le BSIF.
-Pertinence métier : Ce changement met l'accent sur l'amélioration de la transparence des exigences réglementaires en matière de fonds propres. L'ajout de ce tableau permet une meilleure compréhension des attentes réglementaires et facilite la comparabilité entre institutions financières.
-Point de surveillance : Fonds propres réglementaires — Le changement indique une nouvelle divulgation qui améliore la transparence des exigences minimales de fonds propres. Ce point permet de suivre l'évolution des attentes réglementaires et la comparabilité des pratiques de divulgation entre pairs.</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -894,32 +902,24 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>intro</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Exigences - Ratios des fonds propres (1) , de levier (1) et TLAC (2) réglementaires</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>La politique de gestion du capital de la Banque définit les principes directeurs ainsi que les rôles et responsabilités à l'égard de son processus interne d'évaluation de l'adéquation des fonds propres. Ce processus vise à déterminer le niveau des fonds propres dont la Banque doit disposer afin de poursuivre ses activités d'affaires et de faire face aux pertes non prévues découlant de conditions économiques et opérationnelles extrêmement difficiles.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>La Banque gère son capital conformément au cadre de gestion du capital qui est décrit dans la section « Gestion du capital » du Rapport annuel 2025 aux pages 62 à 71.</t>
+          <t>Le tableau suivant présente les exigences minimales de fonds propres établies par le BSIF.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -930,748 +930,848 @@
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Structure du rapport, fonds propres réglementaires.
-Ce qui change : Le texte sur la politique de gestion du capital et le processus d'évaluation des fonds propres a été remplacé par une mention du cadre de gestion du capital.
+Sujet détecté : Information ajoutée, exigences réglementaires.
+Ce qui change : Le T2 ajoute une phrase introductive concernant un tableau des exigences minimales de fonds propres, absente au T1.
+Pertinence métier : Ce changement met en évidence l'ajout d'une divulgation sur les exigences minimales de fonds propres, ce qui peut affecter la compréhension des attentes réglementaires. L'introduction de cette information améliore la transparence sur les exigences de fonds propres réglementaires.
+Point de surveillance : Exigences réglementaires — Le changement indique l'ajout d'une divulgation sur les exigences minimales de fonds propres. Ce point permet de suivre l'évolution de la transparence et de la compréhension des exigences réglementaires.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Exposition maximale au risque de crédit selon les catégories d'actifs de Bâle (1)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Premier trimestre 2026 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Premier trimestre 2026 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Deuxième trimestre 2026 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Deuxième trimestre 2026 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de période.
+Ce qui change : Le T2 met à jour les documents de "Premier trimestre" à "Deuxième trimestre".
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
+Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Ratio de liquidité à court terme</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Le tableau de la page suivante présente les positions moyennes du LCR calculées à partir des observations quotidiennes du trimestre. Le LCR moyen de la Banque au cours du trimestre terminé le 31 janvier 2026 est de 189 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à court terme de la Banque est solide.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Le tableau de la page suivante présente les positions moyennes du LCR calculées à partir des observations quotidiennes du trimestre. Le LCR moyen de la Banque au cours du trimestre terminé le 30 avril 2026 est de 170 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à court terme de la Banque est solide.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de date et de moyen.
+Ce qui change : Le T2 met à jour la date de "janvier" à "avril" et modifie le moyen de "189 %" à "170 %".
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport et une variation chiffrée propre à la banque. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
+Point de surveillance : Mise à jour de période et de moyen — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Au 31 janvier 2026, les actifs liquides de niveau 1 représentent 81 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Au 30 avril 2026, les actifs liquides de niveau 1 représentent 81 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de date.
+Ce qui change : Le T2 met à jour la date de "janvier" à "avril".
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
+Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 31 janvier 2026 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 30 avril 2026 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de date.
+Ce qui change : Le T2 met à jour la date de "janvier" à "avril".
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
+Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Ratio de liquidité à long terme</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 31 janvier 2026 est de 120 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 30 avril 2026 est de 118 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de date et de moyen.
+Ce qui change : Le T2 met à jour la date de "janvier" à "avril" et modifie le moyen de "120 %" à "118 %".
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport et une variation chiffrée propre à la banque. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
+Point de surveillance : Mise à jour de période et de moyen — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Risque environnemental et social</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>La Banque surveille de près l'évolution de la réglementation et participe activement aux divers processus de consultation. En outre, depuis le 1 er novembre 2025, le fait nouveau en matière de réglementation suivant est à considérer.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>La Banque surveille de près l'évolution de la réglementation et participe aux divers processus de consultation. En outre, depuis le 1 er novembre 2025, les faits nouveaux en matière de réglementation suivants sont à considérer.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Reformulation mineure.
+Ce qui change : Le T2 reformule "le fait nouveau" en "les faits nouveaux", indiquant potentiellement plusieurs faits à considérer.
+Pertinence métier : Cette reformulation ne constitue pas une nouvelle idée à surveiller, car elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque. Elle reflète simplement une reformulation mineure.
+Point de surveillance : Reformulation mineure — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Divulgation d'information sur les risques</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Le Rapport annuel 2025, le Rapport aux actionnaires - Premier trimestre 2026 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Le Rapport annuel 2025, le Rapport aux actionnaires - Deuxième trimestre 2026 et les documents d'informations complémentaires y afférant ont pour objectif la présentation de renseignements transparents et de grande qualité concernant les risques, conformément aux recommandations du groupe EDTF du Conseil de stabilité financière. Le tableau suivant présente un sommaire des informations relatives aux 32 recommandations du groupe EDTF ainsi que les pages de référence pour aider les utilisateurs à trouver ces informations.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Mise à jour de période.
+Ce qui change : Le T2 met à jour le rapport de "Premier trimestre" à "Deuxième trimestre".
 Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Exigences - Ratios des fonds propres (1) , de levier (1) et TLAC (2) réglementaires</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Accord de Bâle</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>La Banque veille à ce que ses niveaux de fonds propres excèdent en tout temps les limites minimales relatives aux capitaux propres établies par le BSIF, y compris la RSI. Une structure solide de capital permet à la Banque de couvrir les risques inhérents à ses activités, de soutenir ses secteurs d'exploitation et de protéger sa clientèle.</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>La Banque veille à ce que ses niveaux de fonds propres excèdent en tout temps les exigences minimales de fonds propres établies par le BSIF, y compris la RSI. Une structure solide de capital permet à la Banque de couvrir les risques inhérents à ses activités, de soutenir ses secteurs d'exploitation et de protéger sa clientèle.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Exigences réglementaires, fonds propres réglementaires.
-Ce qui change : Le texte a été modifié pour remplacer 'limites minimales relatives aux capitaux propres' par 'exigences minimales de fonds propres'.
-Pertinence métier : Ce changement met l'accent sur la clarification de la terminologie utilisée pour décrire les exigences de fonds propres. L'utilisation de termes précis et conformes aux attentes réglementaires est essentielle pour assurer la transparence et la comparabilité des divulgations entre institutions financières.
-Point de surveillance : Exigences réglementaires — Le changement indique une clarification terminologique qui améliore la compréhension des exigences minimales de fonds propres. Ce point permet de suivre l'évolution des pratiques de divulgation et la conformité aux attentes réglementaires.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Exposition maximale au risque de crédit selon les catégories d'actifs de Bâle (1)</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Premier trimestre 2026 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Premier trimestre 2026 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Afin de respecter les exigences du BSIF en matière de divulgation relative aux prêts hypothécaires, des renseignements additionnels sont présentés dans les documents intitulés « Informations financières complémentaires - Deuxième trimestre 2026 » et « Informations complémentaires sur les fonds propres réglementaires et informations du Pilier 3 - Deuxième trimestre 2026 » disponibles sur le site Internet de la Banque à l'adresse bnc.ca.</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Le BSIF exige des BISI qu'elles maintiennent un ratio de Capacité totale d'absorption des pertes ( Total Loss Absorbing Capacity ou TLAC) fondé sur les risques d'au moins 25,0 % (incluant la RSI) de l'actif pondéré en fonction des risques et un ratio de levier TLAC d'au moins 7,25 %. Le ratio TLAC se calcule en divisant la TLAC disponible par l'actif pondéré en fonction des risques et le ratio de levier TLAC se calcule en divisant la TLAC disponible par l'exposition totale. Au 31 janvier 2026, la valeur des éléments de passif en circulation faisant l'objet de règlements sur la conversion aux fins de la recapitalisation interne s'élève à 31,6 G$ (26,1 G$ au 31 octobre 2025).</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Le BSIF exige des BISI qu'elles maintiennent un ratio de Capacité totale d'absorption des pertes ( Total Loss Absorbing Capacity ou TLAC) fondé sur les risques d'au moins 25,0 % (incluant la RSI) de l'actif pondéré en fonction des risques et un ratio de levier TLAC d'au moins 7,25 %. Le ratio TLAC se calcule en divisant la TLAC disponible par l'actif pondéré en fonction des risques et le ratio de levier TLAC se calcule en divisant la TLAC disponible par l'exposition totale. Au 30 avril 2026, la valeur des éléments de passif en circulation faisant l'objet de règlements sur la conversion aux fins de la recapitalisation interne s'élève à 29,8 G$ (26,1 G$ au 31 octobre 2025).</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>NON — Nouvel élément à surveiller : Non.
-Sujet détecté : Mise à jour de référence temporelle.
-Ce qui change : Les documents de référence ont été mis à jour pour le deuxième trimestre au lieu du premier trimestre.
-Pertinence métier : Ce changement n'apporte pas de nouvelle information substantielle ou de modification de la posture de la banque. Il s'agit simplement d'une mise à jour temporelle des documents de référence, sans impact sur les exigences réglementaires ou la gestion des risques.
-Point de surveillance : Mise à jour temporelle — Ce point peut être écarté du suivi prioritaire, car il ne modifie pas la substance des divulgations ou des exigences réglementaires.</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Ratio de liquidité à court terme</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Le tableau de la page suivante présente les positions moyennes du LCR calculées à partir des observations quotidiennes du trimestre. Le LCR moyen de la Banque au cours du trimestre terminé le 31 janvier 2026 est de 189 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à court terme de la Banque est solide.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Le tableau de la page suivante présente les positions moyennes du LCR calculées à partir des observations quotidiennes du trimestre. Le LCR moyen de la Banque au cours du trimestre terminé le 30 avril 2026 est de 170 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à court terme de la Banque est solide.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>NON — Nouvel élément à surveiller : Non.
-Sujet détecté : Mise à jour de référence temporelle et chiffrée.
-Ce qui change : Les dates et le pourcentage du moyen ont été modifiés, passant de janvier et à avril et.
-Pertinence métier : Ce changement n'apporte pas de nouvelle information substantielle ou de modification de la posture de la banque. Il s'agit simplement d'une mise à jour temporelle et chiffrée, sans impact sur les exigences réglementaires ou la gestion des risques.
-Point de surveillance : Mise à jour temporelle et chiffrée — Ce point peut être écarté du suivi prioritaire, car il ne modifie pas la substance des divulgations ou des exigences réglementaires.</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Au 31 janvier 2026, les actifs liquides de niveau 1 représentent 81 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Au 30 avril 2026, les actifs liquides de niveau 1 représentent 81 % des HQLA de la Banque, qui comprennent la trésorerie, les dépôts auprès des banques centrales, les obligations émises ou garanties par le gouvernement du Canada et les gouvernements provinciaux du Canada.</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>NON — Nouvel élément à surveiller : Non.
-Sujet détecté : Mise à jour de référence temporelle.
-Ce qui change : La date de référence pour les actifs liquides de niveau a été mise à jour de janvier à avril.
-Pertinence métier : Ce changement n'apporte pas de nouvelle information substantielle ou de modification de la posture de la banque. Il s'agit simplement d'une mise à jour temporelle, sans impact sur les exigences réglementaires ou la gestion des risques.
-Point de surveillance : Mise à jour temporelle — Ce point peut être écarté du suivi prioritaire, car il ne modifie pas la substance des divulgations ou des exigences réglementaires.</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 31 janvier 2026 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Les sorties de trésorerie découlent de l'application d'hypothèses, définies par le BSIF, sur les dépôts, la dette, le financement garanti, les engagements et les exigences de garanties supplémentaires. Les sorties de trésorerie sont en partie contrebalancées par les entrées de trésorerie, qui proviennent principalement de prêts garantis et de prêts performants. La Banque s'attend à ce que les LCR présentés varient d'un trimestre à l'autre, sans que ces variations ne représentent nécessairement une tendance. La variation entre le trimestre terminé le 30 avril 2026 et le trimestre précédent découle du cours normal des activités. Les réserves de liquidités de la Banque dépassent largement le total des sorties nettes de trésorerie.</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>NON — Nouvel élément à surveiller : Non.
-Sujet détecté : Mise à jour de référence temporelle.
-Ce qui change : La date de référence pour la variation des a été mise à jour de janvier à avril.
-Pertinence métier : Ce changement n'apporte pas de nouvelle information substantielle ou de modification de la posture de la banque. Il s'agit simplement d'une mise à jour temporelle, sans impact sur les exigences réglementaires ou la gestion des risques.
-Point de surveillance : Mise à jour temporelle — Ce point peut être écarté du suivi prioritaire, car il ne modifie pas la substance des divulgations ou des exigences réglementaires.</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Ratio de liquidité à long terme</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 31 janvier 2026 est de 120 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Le tableau suivant présente les positions calibrées du NSFR calculées selon la stabilité des passifs et la liquidité des actifs conformément à la ligne directrice Normes de liquidité du BSIF. Le NSFR de la Banque au 30 avril 2026 est de 118 %, bien au-delà de l'exigence réglementaire de 100 %, ce qui démontre que la position de liquidité à long terme de la Banque est solide.</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>NON — Nouvel élément à surveiller : Non.
-Sujet détecté : Mise à jour de référence temporelle et chiffrée.
-Ce qui change : La date de référence pour le est passée du janvier au avril, et le a diminué de à.
-Pertinence métier : Ce changement n'apporte pas de nouvelle information substantielle ou de modification de la posture de la banque. Il s'agit simplement d'une mise à jour temporelle et chiffrée, sans impact sur les exigences réglementaires ou la gestion des risques.
-Point de surveillance : Mise à jour temporelle et chiffrée — Ce point peut être écarté du suivi prioritaire, car il ne modifie pas la substance des divulgations ou des exigences réglementaires.</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Activités de gestion</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Le 25 septembre 2025, la Banque a débuté un programme d'offre publique de rachat à des fins d'annulation dans le cours normal de ses activités, visant jusqu'à concurrence de 8 000 000 d'actions ordinaires (représentant environ 2,04 % des actions ordinaires alors en circulation) au cours de la période de 12 mois se terminant au plus tard le 24 septembre 2026. Au cours du trimestre terminé le 31 janvier 2026, la Banque a effectué le rachat de 3 593 000 actions ordinaires au prix de 619 M$, ce qui a réduit de 90 M$ le Capital-actions ordinaires et de 529 M$ les Résultats non distribués . La Banque a racheté un total de 4 978 400 actions ordinaires dans le cadre de ce programme au prix de 832 M$.</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Le 25 septembre 2025, la Banque a débuté un programme d'offre publique de rachat à des fins d'annulation dans le cours normal de ses activités, visant jusqu'à concurrence de 8 000 000 d'actions ordinaires (représentant environ 2,04 % des actions ordinaires alors en circulation) au cours de la période de 12 mois se terminant au plus tard le 24 septembre 2026. Le 12 mars 2026, une modification à l'offre publique de rachat a pris effet. Cette modification a augmenté le nombre maximal d'actions ordinaires de la Banque émises et en circulation pouvant être rachetées aux fins d'annulation jusqu'à concurrence de 14 500 000 actions ordinaires (représentant environ 3,70 % des actions ordinaires en circulation en date du 11 septembre 2025) au cours de la période de 12 mois se terminant le 24 septembre 2026. Au cours du semestre terminé le 30 avril 2026, la Banque a effectué le rachat de 6 965 400 actions ordinaires au prix de 1 241 M$, ce qui a réduit de 176 M$ le Capital-actions ordinaires et de 1 065 M$ les Résultats non distribués . La Banque a racheté un total de 8 350 800 actions ordinaires dans le cadre de ce programme au prix de 1 454 M$.</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le programme de rachat a été modifié avec une augmentation du nombre maximal d'actions pouvant être rachetées et une mise à jour des chiffres de rachat.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour normale des chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour la date de référence de janvier à avril et la valeur des éléments de passif en circulation, sans modifier le cadre réglementaire ou la méthodologie.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de date et de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>jhjkh</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Dividendes</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Exigences - Ratios des fonds propres (1) , de levier (1) et TLAC (2) réglementaires</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Le 24 février 2026, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,24 $, payable le 1 er mai 2026 aux actionnaires inscrits le 30 mars 2026.</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Le 26 mai 2026, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,32 $ par action ordinaire, en hausse de 8 cents ou 6 %, payable le 1 er août 2026 aux actionnaires inscrits le 29 juin 2026.</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>La Banque veille à ce que ses niveaux de fonds propres excèdent en tout temps les limites minimales relatives aux capitaux propres établies par le BSIF, y compris la RSI. Une structure solide de capital permet à la Banque de couvrir les risques inhérents à ses activités, de soutenir ses secteurs d'exploitation et de protéger sa clientèle.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>La Banque veille à ce que ses niveaux de fonds propres excèdent en tout temps les exigences minimales de fonds propres établies par le BSIF, y compris la RSI. Une structure solide de capital permet à la Banque de couvrir les risques inhérents à ses activités, de soutenir ses secteurs d'exploitation et de protéger sa clientèle.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>NON — Nouvel élément à surveiller : Non.
+Sujet détecté : Reformulation mineure.
+Ce qui change : Le T2 reformule 'limites minimales relatives aux capitaux propres' en 'exigences minimales de fonds propres', sans modifier le fond de la divulgation.
+Pertinence métier : Cette reformulation ne constitue pas une nouvelle idée à surveiller, car elle n'apporte pas de changement substantiel à la divulgation. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Point de surveillance : Reformulation mineure — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Activités de gestion</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Le 25 septembre 2025, la Banque a débuté un programme d'offre publique de rachat à des fins d'annulation dans le cours normal de ses activités, visant jusqu'à concurrence de 8 000 000 d'actions ordinaires (représentant environ 2,04 % des actions ordinaires alors en circulation) au cours de la période de 12 mois se terminant au plus tard le 24 septembre 2026. Au cours du trimestre terminé le 31 janvier 2026, la Banque a effectué le rachat de 3 593 000 actions ordinaires au prix de 619 M$, ce qui a réduit de 90 M$ le Capital-actions ordinaires et de 529 M$ les Résultats non distribués . La Banque a racheté un total de 4 978 400 actions ordinaires dans le cadre de ce programme au prix de 832 M$.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Le 25 septembre 2025, la Banque a débuté un programme d'offre publique de rachat à des fins d'annulation dans le cours normal de ses activités, visant jusqu'à concurrence de 8 000 000 d'actions ordinaires (représentant environ 2,04 % des actions ordinaires alors en circulation) au cours de la période de 12 mois se terminant au plus tard le 24 septembre 2026. Le 12 mars 2026, une modification à l'offre publique de rachat a pris effet. Cette modification a augmenté le nombre maximal d'actions ordinaires de la Banque émises et en circulation pouvant être rachetées aux fins d'annulation jusqu'à concurrence de 14 500 000 actions ordinaires (représentant environ 3,70 % des actions ordinaires en circulation en date du 11 septembre 2025) au cours de la période de 12 mois se terminant le 24 septembre 2026. Au cours du semestre terminé le 30 avril 2026, la Banque a effectué le rachat de 6 965 400 actions ordinaires au prix de 1 241 M$, ce qui a réduit de 176 M$ le Capital-actions ordinaires et de 1 065 M$ les Résultats non distribués . La Banque a racheté un total de 8 350 800 actions ordinaires dans le cadre de ce programme au prix de 1 454 M$.</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : La date de déclaration des dividendes a changé, le montant du dividende par action ordinaire a augmenté de cents ou, et les dates de paiement et d'enregistrement ont été mises à jour.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour normale des chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 modifie l'offre publique de rachat avec une augmentation du nombre d'actions pouvant être rachetées et met à jour les dates et les chiffres concernant les actions rachetées et les montants financiers.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Dividendes</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Au 20 février 2026, le nombre d'actions ordinaires en circulation se chiffre à 387 257 925 et le nombre d'options en cours est de 10 448 488.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Au 22 mai 2026, le nombre d'actions ordinaires en circulation se chiffre à 385 142 589 et le nombre d'options en cours est de 9 969 096.</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Le 24 février 2026, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,24 $, payable le 1 er mai 2026 aux actionnaires inscrits le 30 mars 2026.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Le 26 mai 2026, le conseil d'administration a déclaré les dividendes réguliers sur les diverses séries d'actions privilégiées de premier rang, ainsi qu'un dividende de 1,32 $ par action ordinaire, en hausse de 8 cents ou 6 %, payable le 1 er août 2026 aux actionnaires inscrits le 29 juin 2026.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : La date et les chiffres concernant le nombre d'actions ordinaires et d'options en cours ont été mis à jour.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour normale des chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour la date de déclaration des dividendes, le montant du dividende, la date de paiement et la date d'inscription, sans modifier le cadre réglementaire ou la méthodologie.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de dates et de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 568 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 80,1 % selon le nombre d'actions ordinaires de la Banque en circulation au 31 janvier 2026.</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 559 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 80,2 % selon le nombre d'actions ordinaires de la Banque en circulation au 30 avril 2026.</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Au 20 février 2026, le nombre d'actions ordinaires en circulation se chiffre à 387 257 925 et le nombre d'options en cours est de 10 448 488.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Au 22 mai 2026, le nombre d'actions ordinaires en circulation se chiffre à 385 142 589 et le nombre d'options en cours est de 9 969 096.</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Les chiffres concernant le maximum d'actions ordinaires après conversion et l'effet dilutif ont été mis à jour, ainsi que la date de référence.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour normale des chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour les dates et les chiffres concernant le nombre d'actions ordinaires et d'options en cours, sans modifier le cadre réglementaire ou la méthodologie.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de dates et de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de 0,6 G$ pour s'établir à 189,4 G$ au 31 janvier 2026, comparativement à 188,8 G$ au 31 octobre 2025, une augmentation de 0,6 G$ qui s'explique principalement par la croissance organique de l'actif pondéré en fonction des risques atténuée par la variation du taux de change.</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de 5,7 G$ pour s'établir à 194,5 G$ au 30 avril 2026, comparativement à 188,8 G$ au 31 octobre 2025. Cette augmentation découle de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts atténuées par la variation du taux de change.</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Actions, autres instruments de capitaux propres et options d'achat d'actions</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 568 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 80,1 % selon le nombre d'actions ordinaires de la Banque en circulation au 31 janvier 2026.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Selon un prix-plancher de 5,00 $ et en tenant compte des dividendes et intérêts cumulés estimés, ces instruments de fonds propres assortis d'une clause FPUNV se convertiraient en un maximum de 1 559 millions d'actions ordinaires de la Banque, d'où un effet dilutif de 80,2 % selon le nombre d'actions ordinaires de la Banque en circulation au 30 avril 2026.</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Les chiffres de l'augmentation de l'actif pondéré en fonction des risques ont changé, et la détérioration de la qualité de crédit a été ajoutée comme facteur d'augmentation.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour normale des chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour les chiffres concernant le maximum d'actions ordinaires et l'effet dilutif, ainsi que la date de référence, sans modifier le cadre réglementaire ou la méthodologie.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,7 %, à 15,1 % et à 17,3 % au 31 janvier 2026, comparativement à des ratios de 13,8 %, de 15,1 % et de 17,3 %, respectivement, au 31 octobre 2025. Le ratio des fonds propres CET1 a diminué légèrement depuis le 31 octobre 2025, tandis que le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres sont demeurés stables. Les rachats d'actions ordinaires et la croissance de l'actif pondéré en fonction des risques ont contribué à la baisse des ratios, atténués par le résultat net, déduction faite des dividendes.</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Le ratio des fonds propres CET1, le ratio des fonds propres de catégorie 1 et le ratio du total des fonds propres s'établissent, respectivement, à 13,5 %, à 14,9 % et à 17,0 % au 30 avril 2026, comparativement à des ratios de 13,8 %, de 15,1 % et de 17,3 %, respectivement, au 31 octobre 2025. Tous les ratios de fonds propres ont diminué depuis le 31 octobre 2025. La baisse est principalement attribuable aux rachats d'actions ordinaires à des fins d'annulation et à la croissance de l'actif pondéré en fonction des risques, atténués par le résultat net, déduction faite des dividendes.</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Les valeurs des ratios, de catégorie et du total des fonds propres ont changé, et tous les ratios ont diminué. La raison de la baisse inclut maintenant spécifiquement les rachats d'actions à des fins d'annulation.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour normale des chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
-Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+Ce qui change : Le T2 met à jour les dates et les pourcentages des ratios de fonds propres, sans modifier le cadre réglementaire ou la méthodologie.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Au 31 janvier 2026, le ratio TLAC et le ratio de levier TLAC s'établissent à 32,5 % et à 9,2 %, comparativement à 29,7 % et à 8,8 %, respectivement, au 31 octobre 2025. L'augmentation du ratio TLAC et du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours de la période.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Au 30 avril 2026, le ratio TLAC et le ratio de levier TLAC s'établissent à 31,5 % et à 9,0 %, comparativement à 29,7 % et à 8,8 %, respectivement, au 31 octobre 2025. L'augmentation du ratio TLAC et du ratio de levier TLAC s'explique principalement par les émissions nettes d'instruments qui satisfont tous les critères d'admissibilité TLAC au cours de la période.</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Les valeurs des ratios et de levier ont changé.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour normale des chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
-Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+Ce qui change : Le T2 met à jour les dates et les pourcentages des ratios TLAC et de levier, sans modifier le cadre réglementaire ou la méthodologie.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Gestion du capital</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Ratios des fonds propres réglementaires, de levier et TLAC</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Au cours du trimestre terminé le 31 janvier 2026, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Au cours du trimestre et du semestre terminés le 30 avril 2026, la Banque a respecté toutes les exigences réglementaires imposées par le BSIF en matière de capital, de levier et de TLAC.</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Ajout de la mention du respect des exigences pour le semestre en plus du trimestre.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour normale des chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour la date et ajoute la mention du semestre, sans modifier le cadre réglementaire ou la méthodologie.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de dates et de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/bnc/2026_t2_vs_2026_t1/text_comparison.xlsx
+++ b/outputs/resultats/bnc/2026_t2_vs_2026_t1/text_comparison.xlsx
@@ -552,7 +552,7 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Nouvelle mention réglementaire, risque climatique / ESG, information ajoutée.
-Ce qui change : Le T2 ajoute une divulgation sur la législation « Omnibus » de la Commission européenne et son impact sur la directive CSRD, absente au T1.
+Ce qui change : Le T2 ajoute une divulgation sur la législation « Omnibus » de la Commission européenne et son impact sur la divulgation en matière de durabilité, absente au T1.
 Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
@@ -596,7 +596,7 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Nouvelle mention réglementaire, risque climatique / ESG, information ajoutée.
-Ce qui change : Le T2 ajoute une divulgation sur les modifications proposées par le CCNID concernant les informations à fournir en lien avec les émissions de gaz à effet de serre, absente au T1.
+Ce qui change : Le T2 ajoute une divulgation sur le projet de modification de la NCID par le CCNID et les consultations en cours, absente au T1.
 Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
@@ -641,9 +641,9 @@
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Information retirée, exigences réglementaires.
-Ce qui change : Le T2 retire la sous-section sur les exigences de communication publique pour les banques d'importance systémique mondiale, présente au T1.
-Pertinence métier : Ce changement met l'accent sur la réduction de la divulgation relative aux exigences de communication publique pour les banques d'importance systémique mondiale. Le retrait de cette information modifie la lecture de la transparence de la banque sur ses obligations réglementaires, ce qui est crucial pour la comparabilité entre pairs.
-Point de surveillance : Exigences réglementaires — Le changement indique un retrait de la divulgation sur les exigences de communication publique pour les banques d'importance systémique mondiale. Ce point permet de suivre l'évolution de la transparence de la banque sur ses obligations réglementaires et la comparabilité de sa divulgation avec les autres institutions.</t>
+Ce qui change : Le T2 retire une sous-section entière sur les exigences de communication publique pour les banques d'importance systémique mondiale, présente au T1.
+Pertinence métier : Ce changement met l'accent sur la réduction de la transparence concernant les obligations de communication publique pour les banques d'importance systémique. Le retrait de cette information peut affecter la compréhension des exigences réglementaires et la comparabilité entre pairs, ce qui est crucial pour l'évaluation des risques et la conformité.
+Point de surveillance : Exigences de communication publique — Le changement indique que la banque réduit le niveau de détail fourni sur les obligations de communication publique. Ce point permet de suivre l'impact de cette réduction sur la transparence et la comparabilité des pratiques de communication entre institutions.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -651,22 +651,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>VaR des portefeuilles de négociation (1) (2)</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>La moyenne de la VaR totale des portefeuilles de négociation est demeurée relativement stable entre le quatrième trimestre de 2025 et le premier trimestre de 2026.</t>
+          <t>La Gestion du capital assume le double rôle d'assurer un rendement concurrentiel aux actionnaires de la Banque tout en préservant de solides assises financières afin de couvrir les risques inhérents aux activités de la Banque, de soutenir les secteurs d'exploitation et de protéger la clientèle. La politique de gestion du capital de la Banque définit les principes directeurs ainsi que les rôles et responsabilités à l'égard de son processus interne d'évaluation de l'adéquation des fonds propres. Ce processus vise à déterminer le niveau des fonds propres dont la Banque doit disposer afin de poursuivre ses activités d'affaires et de faire face aux pertes non prévues découlant de conditions économiques et opérationnelles extrêmement difficiles. Plus de détails sur le cadre de gestion du capital sont présentés dans la section « Gestion du capital » du Rapport annuel 2025 aux pages 62 à 71.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>La moyenne de la VaR totale des portefeuilles de négociation a diminué entre le premier et le deuxième trimestre de 2026, principalement en raison d'une baisse du risque de taux d'intérêt.</t>
+          <t>La Gestion du capital assume le double rôle d'assurer un rendement concurrentiel aux actionnaires de la Banque tout en préservant de solides assises financières afin de couvrir les risques inhérents aux activités de la Banque, de soutenir les secteurs d'exploitation et de protéger la clientèle. La Banque gère son capital conformément au cadre de gestion du capital qui est décrit dans la section « Gestion du capital » du Rapport annuel 2025 aux pages 62 à 71.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -692,10 +692,10 @@
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Texte de risque modifié, hypothèses ou explications de risque.
-Ce qui change : Le T2 précise que la diminution de la mesure de risque de marché est principalement due à une baisse du risque de taux d'intérêt, ce qui n'était pas mentionné au T1.
-Pertinence métier : Ce changement met en évidence une révision des explications fournies par la banque concernant la gestion de son risque de marché. La mention explicite de la baisse du risque de taux d'intérêt modifie la lecture de l'exposition au risque et la transparence de la banque sur ses facteurs de risque.
-Point de surveillance : Risque de marché — Le changement indique que la banque ajuste ses explications sur la variation de la mesure de risque de marché. Ce point permet de suivre l'évolution de la transparence de la banque sur ses risques de marché et la comparabilité de sa divulgation avec les autres institutions.</t>
+Sujet détecté : Méthode de calcul ou approche modifiée, fonds propres réglementaires.
+Ce qui change : Le T2 supprime la description détaillée du processus interne d'évaluation de l'adéquation des fonds propres, se concentrant sur le cadre de gestion du capital.
+Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
+Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -708,17 +708,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La politique de gestion du capital de la Banque définit les principes directeurs ainsi que les rôles et responsabilités à l'égard de son processus interne d'évaluation de l'adéquation des fonds propres. Ce processus vise à déterminer le niveau des fonds propres dont la Banque doit disposer afin de poursuivre ses activités d'affaires et de faire face aux pertes non prévues découlant de conditions économiques et opérationnelles extrêmement difficiles. Plus de détails sur le cadre de gestion du capital sont présentés dans la section « Gestion du capital » du Rapport annuel 2025 aux pages 62 à 71.</t>
+          <t>L'actif pondéré en fonction des risques a augmenté de 0,6 G$ pour s'établir à 189,4 G$ au 31 janvier 2026, comparativement à 188,8 G$ au 31 octobre 2025, une augmentation de 0,6 G$ qui s'explique principalement par la croissance organique de l'actif pondéré en fonction des risques atténuée par la variation du taux de change.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>La Banque gère son capital conformément au cadre de gestion du capital qui est décrit dans la section « Gestion du capital » du Rapport annuel 2025 aux pages 62 à 71.</t>
+          <t>L'actif pondéré en fonction des risques a augmenté de 5,7 G$ pour s'établir à 194,5 G$ au 30 avril 2026, comparativement à 188,8 G$ au 31 octobre 2025. Cette augmentation découle de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts atténuées par la variation du taux de change.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -742,64 +742,56 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Texte de risque modifié, fonds propres réglementaires.
-Ce qui change : Le T2 simplifie la description du cadre de gestion du capital, supprimant des détails sur le processus interne d'évaluation des fonds propres et les pertes non prévues.
-Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
-Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Actif pondéré en fonction des risques selon les principaux facteurs de risque</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de 0,6 G$ pour s'établir à 189,4 G$ au 31 janvier 2026, comparativement à 188,8 G$ au 31 octobre 2025, une augmentation de 0,6 G$ qui s'explique principalement par la croissance organique de l'actif pondéré en fonction des risques atténuée par la variation du taux de change.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>L'actif pondéré en fonction des risques a augmenté de 5,7 G$ pour s'établir à 194,5 G$ au 30 avril 2026, comparativement à 188,8 G$ au 31 octobre 2025. Cette augmentation découle de la croissance organique de l'actif pondéré en fonction des risques et de la détérioration de la qualité de crédit du portefeuille de prêts atténuées par la variation du taux de change.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Texte de risque modifié, fonds propres réglementaires.
 Ce qui change : Le T2 ajoute la détérioration de la qualité de crédit comme facteur d'augmentation de l'actif pondéré en fonction des risques, absente au T1.
-Pertinence métier : Ce changement met en évidence un nouveau facteur de risque influençant l'actif pondéré en fonction des risques, ce qui peut affecter la compréhension des risques liés aux fonds propres réglementaires. L'ajout de la détérioration de la qualité de crédit modifie la lecture des facteurs influençant l'actif pondéré en fonction des risques.
-Point de surveillance : Fonds propres réglementaires — Le changement indique l'ajout d'un nouveau facteur de risque influençant l'actif pondéré en fonction des risques. Ce point permet de suivre l'évolution de la compréhension des risques liés aux fonds propres réglementaires.</t>
+Pertinence métier : Ce changement met l'accent sur l'ajout d'un facteur de risque lié à la qualité de crédit, ce qui peut affecter la gestion des fonds propres et la perception du risque par les parties prenantes. L'introduction de ce facteur est importante pour évaluer la stabilité financière et la gestion des risques de la banque.
+Point de surveillance : Qualité de crédit — Le changement indique que la banque reconnaît désormais la détérioration de la qualité de crédit comme un facteur d'augmentation de l'actif pondéré en fonction des risques. Ce point permet de suivre l'impact de ce facteur sur la gestion des fonds propres et la stabilité financière de la banque.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Revenus de négociation et de souscription quotidiens</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Le graphique suivant illustre les revenus de négociation et de souscription ainsi que la VaR sur une base quotidienne. Les revenus de négociation et de souscription quotidiens ont été positifs pendant 93 % des jours du trimestre terminé le 31 janvier 2026. De plus, quatre jours ont été marqués par des pertes nettes de négociation et de souscription quotidiennes supérieures à 1 M$. Aucune de ces pertes n'excédait la VaR.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Structure du rapport, information retirée.
+Ce qui change : Le T2 retire une sous-section entière sur les revenus de négociation et de souscription quotidiens, qui était présente au T1.
+Pertinence métier : Ce changement met en évidence une modification dans la structure du rapport, ce qui peut affecter la transparence et la comparabilité des informations sur les performances de négociation. Le retrait de cette divulgation peut influencer la perception de la performance financière de la banque.
+Point de surveillance : Structure du rapport — Le changement indique une modification dans la présentation des informations de performance, nécessitant une attention particulière sur la transparence et la comparabilité des divulgations financières.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -812,12 +804,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Revenus de négociation et de souscription quotidiens</t>
+          <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -827,71 +819,79 @@
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Le graphique suivant illustre les revenus de négociation et de souscription ainsi que la VaR sur une base quotidienne. Les revenus de négociation et de souscription quotidiens ont été positifs pendant 93 % des jours du trimestre terminé le 31 janvier 2026. De plus, quatre jours ont été marqués par des pertes nettes de négociation et de souscription quotidiennes supérieures à 1 M$. Aucune de ces pertes n'excédait la VaR.</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Structure du rapport, information retirée.
-Ce qui change : Le T2 retire une sous-section sur les revenus de négociation et de souscription quotidiens, présente au T1.
-Pertinence métier : Ce changement met l'accent sur la modification de la structure du rapport et la réduction de la transparence sur les performances de négociation de la banque. Le retrait d'une section entière peut affecter la compréhension des activités de négociation et la comparabilité avec les pairs.
-Point de surveillance : Structure du rapport — Le changement indique que la banque réduit la divulgation de ses performances de négociation. Ce point permet de suivre l'évolution de la transparence de la banque sur ses activités de négociation et la comparabilité de sa divulgation avec les autres institutions.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Gestion des risques</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Les tableaux suivants présentent les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan au 31 janvier 2026, ainsi que les données comparatives au 31 octobre 2025. Les informations recueillies dans le cadre de cette analyse des échéances constituent une composante de la gestion des liquidités et du financement. Cependant, cette répartition par échéance n'est pas représentative de la façon dont la Banque gère son risque de taux d'intérêt, ni son risque de liquidité ni ses besoins de financement. La Banque tient compte de facteurs autres que les échéances contractuelles lorsqu'elle évalue les actifs liquides ou les flux de trésorerie futurs prévus.
 Dans le cours normal de ses activités, la Banque prend divers engagements hors bilan. Les instruments de crédit utilisés pour répondre aux besoins de financement de sa clientèle représentent le montant maximal du crédit additionnel que la Banque peut devoir consentir si les engagements sont entièrement utilisés.
 La Banque a également des engagements minimaux futurs, en vertu de contrats de location, et d'autres contrats, principalement liés à des engagements d'achat de prêts et à des services informatiques impartis.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
 Sujet détecté : Structure du rapport, information retirée.
-Ce qui change : Le T2 retire une sous-section sur les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan, présente au T1.
+Ce qui change : Le T2 retire une sous-section entière sur les échéances contractuelles résiduelles des éléments du bilan et des engagements hors bilan, qui était présente au T1.
 Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
       </c>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>VaR des portefeuilles de négociation (1) (2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>La moyenne de la VaR totale des portefeuilles de négociation est demeurée relativement stable entre le quatrième trimestre de 2025 et le premier trimestre de 2026.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>La moyenne de la VaR totale des portefeuilles de négociation a diminué entre le premier et le deuxième trimestre de 2026, principalement en raison d'une baisse du risque de taux d'intérêt.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>OUI — Nouvel élément à surveiller : Oui.
+Sujet détecté : Texte de risque modifié.
+Ce qui change : Le T2 indique une diminution de la mesure de risque de marché totale des portefeuilles de négociation, principalement en raison d'une baisse du risque de taux d'intérêt, alors qu'elle était stable au T1.
+Pertinence métier : Ce changement met en évidence une modification dans l'évaluation du risque de marché, ce qui peut influencer la perception de la stabilité financière de la banque. La mention d'une baisse du risque de taux d'intérêt introduit un nouvel élément à surveiller dans l'analyse des risques de marché.
+Point de surveillance : Risque de marché — Le changement indique une variation dans l'évaluation du risque de marché, nécessitant une attention particulière sur les facteurs influençant cette mesure, notamment le risque de taux d'intérêt.</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -930,10 +930,10 @@
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>OUI — Nouvel élément à surveiller : Oui.
-Sujet détecté : Information ajoutée, exigences réglementaires.
+Sujet détecté : Information ajoutée, fonds propres réglementaires.
 Ce qui change : Le T2 ajoute une phrase introductive concernant un tableau des exigences minimales de fonds propres, absente au T1.
-Pertinence métier : Ce changement met en évidence l'ajout d'une divulgation sur les exigences minimales de fonds propres, ce qui peut affecter la compréhension des attentes réglementaires. L'introduction de cette information améliore la transparence sur les exigences de fonds propres réglementaires.
-Point de surveillance : Exigences réglementaires — Le changement indique l'ajout d'une divulgation sur les exigences minimales de fonds propres. Ce point permet de suivre l'évolution de la transparence et de la compréhension des exigences réglementaires.</t>
+Pertinence métier : Ce changement met en évidence l'ajout d'une divulgation sur les exigences minimales de fonds propres, ce qui peut améliorer la transparence et la compréhension des attentes réglementaires. L'introduction de cette information est importante pour évaluer la conformité et la gestion des fonds propres par la banque.
+Point de surveillance : Exigences minimales de fonds propres — Le changement indique que la banque fournit désormais une information supplémentaire sur les exigences minimales de fonds propres. Ce point permet de suivre l'évolution de la transparence et de la comparabilité des pratiques de gestion des fonds propres entre institutions.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -983,9 +983,9 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de période.
-Ce qui change : Le T2 met à jour les documents de "Premier trimestre" à "Deuxième trimestre".
-Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
-Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+Ce qui change : Le T2 met à jour les références de "Premier trimestre" à "Deuxième trimestre" dans les documents de divulgation.
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement une mise à jour de période sans impact sur le contenu ou la substance des divulgations réglementaires. Elle ne modifie pas les exigences réglementaires, les méthodes de calcul ou la posture de risque.
+Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
       <c r="I12" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
-Sujet détecté : Mise à jour de date et de moyen.
-Ce qui change : Le T2 met à jour la date de "janvier" à "avril" et modifie le moyen de "189 %" à "170 %".
-Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport et une variation chiffrée propre à la banque. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
-Point de surveillance : Mise à jour de période et de moyen — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+Sujet détecté : Mise à jour de date.
+Ce qui change : Le T2 met à jour la date de "janvier" à "avril" dans la présentation des positions moyennes de liquidité.
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement une mise à jour de date sans impact sur le contenu ou la substance des divulgations réglementaires. Elle ne modifie pas les exigences réglementaires, les méthodes de calcul ou la posture de risque.
+Point de surveillance : Mise à jour de date — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -1087,9 +1087,9 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de date.
-Ce qui change : Le T2 met à jour la date de "janvier" à "avril".
-Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
-Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+Ce qui change : Le T2 met à jour la date de "janvier" à "avril" dans la présentation des actifs liquides de niveau 1.
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement une mise à jour de date sans impact sur le contenu ou la substance des divulgations réglementaires. Elle ne modifie pas les exigences réglementaires, les méthodes de calcul ou la posture de risque.
+Point de surveillance : Mise à jour de date — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
@@ -1139,9 +1139,9 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de date.
-Ce qui change : Le T2 met à jour la date de "janvier" à "avril".
-Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
-Point de surveillance : Mise à jour de période — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+Ce qui change : Le T2 met à jour la date de "janvier" à "avril" dans la présentation des sorties de trésorerie.
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement une mise à jour de date sans impact sur le contenu ou la substance des divulgations réglementaires. Elle ne modifie pas les exigences réglementaires, les méthodes de calcul ou la posture de risque.
+Point de surveillance : Mise à jour de date — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
       <c r="I15" s="3" t="inlineStr">
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
-Sujet détecté : Mise à jour de date et de moyen.
-Ce qui change : Le T2 met à jour la date de "janvier" à "avril" et modifie le moyen de "120 %" à "118 %".
-Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement le changement de période de rapport et une variation chiffrée propre à la banque. Elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque.
-Point de surveillance : Mise à jour de période et de moyen — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+Sujet détecté : Mise à jour de date.
+Ce qui change : Le T2 met à jour la date de "janvier" à "avril" dans la présentation des positions calibrées de liquidité.
+Pertinence métier : Cette mise à jour ne constitue pas une nouvelle idée à surveiller, car elle reflète simplement une mise à jour de date sans impact sur le contenu ou la substance des divulgations réglementaires. Elle ne modifie pas les exigences réglementaires, les méthodes de calcul ou la posture de risque.
+Point de surveillance : Mise à jour de date — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
@@ -1244,8 +1244,8 @@
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Reformulation mineure.
 Ce qui change : Le T2 reformule "le fait nouveau" en "les faits nouveaux", indiquant potentiellement plusieurs faits à considérer.
-Pertinence métier : Cette reformulation ne constitue pas une nouvelle idée à surveiller, car elle ne modifie pas la substance de la divulgation ni n'introduit de nouveaux éléments réglementaires ou de risque. Elle reflète simplement une reformulation mineure.
-Point de surveillance : Reformulation mineure — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de méthode, de conformité ou de posture de risque.</t>
+Pertinence métier : Cette reformulation ne constitue pas une nouvelle idée à surveiller, car elle ne modifie pas le contenu ou la substance des divulgations réglementaires. Elle ne change pas les exigences réglementaires, les méthodes de calcul ou la posture de risque.
+Point de surveillance : Reformulation mineure — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
@@ -1295,7 +1295,7 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour de période.
-Ce qui change : Le T2 met à jour le rapport de "Premier trimestre" à "Deuxième trimestre".
+Ce qui change : Le T2 met à jour les références de "Premier trimestre" à "Deuxième trimestre" dans les documents de divulgation.
 Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
 Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
         </is>
@@ -1347,8 +1347,8 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le T2 met à jour la date de référence de janvier à avril et la valeur des éléments de passif en circulation, sans modifier le cadre réglementaire ou la méthodologie.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de date et de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour la date de référence et la valeur des éléments de passif en circulation pour la recapitalisation interne.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque sans impact sur les exigences réglementaires ou la méthodologie de calcul.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
@@ -1399,8 +1399,8 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Reformulation mineure.
-Ce qui change : Le T2 reformule 'limites minimales relatives aux capitaux propres' en 'exigences minimales de fonds propres', sans modifier le fond de la divulgation.
-Pertinence métier : Cette reformulation ne constitue pas une nouvelle idée à surveiller, car elle n'apporte pas de changement substantiel à la divulgation. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 reformule 'limites minimales relatives aux capitaux propres' en 'exigences minimales de fonds propres'.
+Pertinence métier : Cette reformulation ne constitue pas une nouvelle idée à surveiller, car elle n'apporte pas de changement substantiel à la divulgation. Elle ne modifie pas la compréhension des exigences réglementaires ou la posture de la banque.
 Point de surveillance : Reformulation mineure — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
@@ -1451,8 +1451,8 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le T2 modifie l'offre publique de rachat avec une augmentation du nombre d'actions pouvant être rachetées et met à jour les dates et les chiffres concernant les actions rachetées et les montants financiers.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour les chiffres concernant le programme d'offre publique de rachat et les montants financiers associés.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque sans impact sur les exigences réglementaires ou la méthodologie de calcul.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
@@ -1503,8 +1503,8 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le T2 met à jour la date de déclaration des dividendes, le montant du dividende, la date de paiement et la date d'inscription, sans modifier le cadre réglementaire ou la méthodologie.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de dates et de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour la date de déclaration, le montant du dividende, la date de paiement et la date d'inscription.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque sans impact sur les exigences réglementaires ou la méthodologie de calcul.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
@@ -1555,8 +1555,8 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le T2 met à jour les dates et les chiffres concernant le nombre d'actions ordinaires et d'options en cours, sans modifier le cadre réglementaire ou la méthodologie.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de dates et de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour les chiffres concernant le nombre d'actions ordinaires en circulation et le nombre d'options en cours.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque sans impact sur les exigences réglementaires ou la méthodologie de calcul.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
@@ -1607,8 +1607,8 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le T2 met à jour les chiffres concernant le maximum d'actions ordinaires et l'effet dilutif, ainsi que la date de référence, sans modifier le cadre réglementaire ou la méthodologie.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 met à jour les chiffres concernant le maximum d'actions convertibles et l'effet dilutif, ainsi que la date de référence.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque sans impact sur les exigences réglementaires ou la méthodologie de calcul.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
@@ -1659,9 +1659,9 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le T2 met à jour les dates et les pourcentages des ratios de fonds propres, sans modifier le cadre réglementaire ou la méthodologie.
-Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
-Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
+Ce qui change : Le T2 met à jour les valeurs des ratios de fonds propres et précise que tous les ratios ont diminué.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque sans impact sur les exigences réglementaires ou la méthodologie de calcul.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -1711,9 +1711,9 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le T2 met à jour les dates et les pourcentages des ratios TLAC et de levier, sans modifier le cadre réglementaire ou la méthodologie.
-Pertinence métier : Ce changement met l'accent sur l'évolution du cadre réglementaire applicable aux divulgations climatiques des institutions financières. La mise à jour de la ligne directrice B-15 par le BSIF, notamment le report des exigences liées aux émissions de GES de portée 3, peut influencer la manière dont les banques planifient leur conformité, structurent leurs contrôles ESG et communiquent leurs risques climatiques. Ce point est important à suivre, car il permet d'évaluer l'évolution des attentes prudentielles, la comparabilité des pratiques de divulgation entre pairs et le niveau de préparation des banques face aux exigences climatiques.
-Point de surveillance : Risque climatique / ESG — Le changement indique que la banque tient compte de la mise à jour de la ligne directrice B-15 du BSIF et du report des exigences liées aux émissions de GES de portée 3. Ce point permet de suivre l'adaptation des banques aux attentes prudentielles climatiques, leur niveau de préparation ESG et la comparabilité de leurs pratiques de divulgation entre pairs.</t>
+Ce qui change : Le T2 met à jour les valeurs des ratios et de levier avec de nouvelles valeurs et une nouvelle date.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque sans impact sur les exigences réglementaires ou la méthodologie de calcul.
+Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
@@ -1763,8 +1763,8 @@
         <is>
           <t>NON — Nouvel élément à surveiller : Non.
 Sujet détecté : Mise à jour quantitative propre à la banque.
-Ce qui change : Le T2 met à jour la date et ajoute la mention du semestre, sans modifier le cadre réglementaire ou la méthodologie.
-Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de dates et de chiffres propres à la banque. Elle ne modifie aucun seuil prudentiel, aucune règle BSIF ou AMF, aucune méthode de calcul et aucune posture de risque qui changerait la lecture réglementaire ou la comparabilité métier.
+Ce qui change : Le T2 inclut le respect des exigences pour le trimestre et le semestre, avec une mise à jour de la date.
+Pertinence métier : Cette variation ne constitue pas une nouvelle idée à surveiller, car elle reflète une mise à jour de chiffres propres à la banque sans impact sur les exigences réglementaires ou la méthodologie de calcul.
 Point de surveillance : Mise à jour quantitative — La substance de la divulgation demeure stable. Ce point peut être écarté du suivi prioritaire, sauf si une autre information indique un changement de seuil prudentiel, de méthode, de conformité ou de posture de risque.</t>
         </is>
       </c>
